--- a/JobIntel/sql/query_results/skills_by_role_data_analyst.xlsx
+++ b/JobIntel/sql/query_results/skills_by_role_data_analyst.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42a4dbeb8f84b5af/Desktop/AI-Powered-Job-Market-Intelligence-Platform/AI-Powered-Job-Market-Intelligence-Platform/JobIntel/sql/query_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F8C54F4-9D67-4817-AF16-D6049C346CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{0F8C54F4-9D67-4817-AF16-D6049C346CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF4761F3-48BA-4F42-97F6-4492BE5E06E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80045F16-D308-4093-A011-E41305314D37}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>sql</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>project management</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>demand</t>
   </si>
 </sst>
 </file>
@@ -430,68 +436,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BE04AE-1B23-4B1F-9064-B71C95383A97}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>248</v>
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>158</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>87</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>83</v>
@@ -499,58 +505,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>39</v>
+      <c r="B16">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
